--- a/data/store_openings.xlsx
+++ b/data/store_openings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1428,6 +1428,996 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>しぶそば自由が丘店</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.shibusoba.com/post/jyugaokaopen</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>9/10ザ・ビッグエクスプレスみよし店</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>近江ちゃんぽん亭 岩出店</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://dreamfoods.co.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>9/1オーケー高槻赤大路店(大阪府高槻市)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fOy</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>9/1 ライフ鎌倉梶原店</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>9/3 サンディ吹田五月が丘店(大阪府吹田市)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fPd</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>9/3改装 スーパーのアオキ直江津店(新潟県上越市)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g2v</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>9/3スギ薬局茜部南店(岐阜市)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g2N</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>9/4クックマート上西店（静岡県浜松市）</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g7N</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>9/4(9/3プレ)スーパー生鮮館TAIGA桂子田店</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>9/4改装 名古屋PARCO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>9/4改装 メイチカ(名古屋市)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g7g</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>9/4ウルフギャングステーキハウス名古屋店</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1eZr</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>9/4 ゴジラ・ストア Nagoya</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fn6</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>9/4ロピア彦根ナフコ店</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fNK</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>9/10改装 マルナカ檀紙店(香川県高松市)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g7X</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>9/10ファミリーマート中津川下野店</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g84</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>9/11スーパーマーケットバロー豊中島江店</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fXN</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>9/16SANYO Style STORE PLUS イオンモール岡崎店</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fEw</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>9/17ロピア ムサシ新潟西店(新潟市)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g6X</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>&lt;10/27予定&gt;スーパーマーケットバロー大府北山店</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1e1p</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>10/29 オーケー長吉店(大阪市)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1eUx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>&lt;11/28予定&gt;ドラッグコスモス印場橋店(愛知県)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1e1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>&lt;1/29予定&gt; ザ・ビッグエクストラ関店(岐阜県関市)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1eOu</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>業務スーパー秋田保戸野店2026年7月30日オープン,【1.9万表示】2026/07/</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://x.com/shokusaijp_TMGP/status/2081561660947677395</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>9月1日(火)OPEN！「KINUJO」の世界観を五感で楽しむ『KINUJO Cafe &amp; Bar』が銀座の地に誕生。洗練されたインテリアと美食が融合した特別な体験をお届けいたします。</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000048.000094687.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>【2026年9月3日(木)オープン】全国の名品・銘菓を集めた新店舗「日本めぐり はくまる庵」が誕生</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000003.000188020.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>A5黒毛和牛をひつまぶしスタイルで味わう新ランチが誕生。「薪焼きともつ鍋 桂香-KEIKA- 博多西中洲」にて、7月20日（月）より『A5黒毛和牛の博多牛まぶし』の提供を開始</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000019.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>【大阪・天王寺に山椒まぜそば登場】痺れと香りを極めた山椒まぜそば専門店『麺処 山椒』が2026年7月25日（土）グランドオープン！</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000015.000055652.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>新潟市内、フレスポ赤道に登場！ナポリタン専門店「スパゲッティーのパンチョ 新潟赤道店」が7月17日（金）に新規開店、3連続オープニングキャンペーンを開催</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000105.000117096.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>新潟市南区に「あくあしょっぷ　ぎんなん」7月7日OPEN｜海水魚・水草・生体を扱う、小さく始められるアクアリウム専門店</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000002.000186660.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>【オープン記念としておすすめコースに飲み放題を無料提供】香りを愉しむ新業態「薪焼きともつ鍋 桂香-KEIKA- 博多西中洲」が7月6日（月）グランドオープン！7月1日（水）よりプレオープン</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000018.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>栃木初上陸、全国50店舗目の節目を飾る！ナポリタン専門店「スパゲッティーのパンチョ 宇都宮戸祭店」が7月3日（金）に新規開店、3連続オープニングキャンペーンを開催</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000103.000117096.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>【生ビール・角ハイボール・鬼おろしレモンサワー78円】旬を摘まむオトナ酒場「酒と肴 菜の華(なのはな) 銀座通り店」が6月1日(月)グランドオープン！6月30日(火)まで一部ドリンクを破格でご提供！</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000017.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>【和食さと】広島県に初出店！「和食さと広島観音新町店」を2026年5月22日（金）グランドオープン！</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000899.000122416.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>9月1日(火)OPEN！「KINUJO」の世界観を五感で楽しむ『KINUJO Cafe &amp; Bar』が銀座の地に誕生。洗練されたインテリアと美食が融合した特別な体験をお届けいたします。</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000048.000094687.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>【2026年9月3日(木)オープン】全国の名品・銘菓を集めた新店舗「日本めぐり はくまる庵」が誕生</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000003.000188020.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>A5黒毛和牛をひつまぶしスタイルで味わう新ランチが誕生。「薪焼きともつ鍋 桂香-KEIKA- 博多西中洲」にて、7月20日（月）より『A5黒毛和牛の博多牛まぶし』の提供を開始</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000019.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>【大阪・天王寺に山椒まぜそば登場】痺れと香りを極めた山椒まぜそば専門店『麺処 山椒』が2026年7月25日（土）グランドオープン！</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000015.000055652.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>新潟市内、フレスポ赤道に登場！ナポリタン専門店「スパゲッティーのパンチョ 新潟赤道店」が7月17日（金）に新規開店、3連続オープニングキャンペーンを開催</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000105.000117096.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>新潟市南区に「あくあしょっぷ　ぎんなん」7月7日OPEN｜海水魚・水草・生体を扱う、小さく始められるアクアリウム専門店</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000002.000186660.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>【オープン記念としておすすめコースに飲み放題を無料提供】香りを愉しむ新業態「薪焼きともつ鍋 桂香-KEIKA- 博多西中洲」が7月6日（月）グランドオープン！7月1日（水）よりプレオープン</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000018.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>栃木初上陸、全国50店舗目の節目を飾る！ナポリタン専門店「スパゲッティーのパンチョ 宇都宮戸祭店」が7月3日（金）に新規開店、3連続オープニングキャンペーンを開催</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000103.000117096.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>【生ビール・角ハイボール・鬼おろしレモンサワー78円】旬を摘まむオトナ酒場「酒と肴 菜の華(なのはな) 銀座通り店」が6月1日(月)グランドオープン！6月30日(火)まで一部ドリンクを破格でご提供！</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000017.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026年09月06日</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>【和食さと】広島県に初出店！「和食さと広島観音新町店」を2026年5月22日（金）グランドオープン！</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000899.000122416.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/store_openings.xlsx
+++ b/data/store_openings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2418,6 +2418,1326 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>9/10とりせん田沼インター店(栃木県佐野市)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g9g</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>暮らしと不動産の窓口 K-LIVING ESTATE</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://kl-estate.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>おたからや 上野マルイ店</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.otakaraya.jp/shop/ueno-m/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>アトリエうかい Cafe &amp; Factory HACHIOJI</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.ukai.co.jp/atelier/cafe-factory/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>焼肉 塩ホルモン 好ちゃん 神田本店</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://selecao.co.jp/ourshops/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>エリックサウス</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://enso.ne.jp/erick-south/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>和食日和 おさけと 大手町</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.osaketo-washoku.jp/shop/otemachi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ブラッスリー・ローデンバッハ</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.rodenbach.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ドトールコーヒーショップ 大手町ゲートビルディング店</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.doutor.co.jp/dcs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>大衆とり酒場 とりいちず 大森東口店</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://toriichizu.net/shoplist/4044/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>壱角家 八重洲店</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://gardengroup.co.jp/brand/ichikakuya/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>IL BISONTE 玉川高島屋S・C店</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.ilbisonte.jp/shops/kanto?c=tamagawa_takashimaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Meet＆Meat produced by 相席屋</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://section-8.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>スターバックス コーヒー 長野若槻店</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://store.starbucks.co.jp/detail-4623/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>かにじぇんぬ 金沢</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kani.kanazawa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>VIENT（ビエント）近江八幡店</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://vient-pilates.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>牛角焼肉食堂＆ホルモン酒場 阪神梅田本店スナックパーク店</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.reins.co.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>近江ちゃんぽん亭 岩出店</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://chanpontei.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ワッツウィズ河南町キリン堂店</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.watts-jp.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>10/9TAKENOKO＋byFOODSMARKETsatakeビエラ千里丘</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g98</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>百十四銀行 坂出支店</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.114bank.co.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>牛角焼肉食堂 ゆめタウン久留米店</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://gyukakuyakinikushokudou.ne.jp/store/detail/?id=yumetownkurume</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>9/1オーケー高槻赤大路店(大阪府高槻市)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fOy</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>9/1 ライフ鎌倉梶原店</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>9/3 サンディ吹田五月が丘店(大阪府吹田市)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fPd</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>9/3改装 スーパーのアオキ直江津店(新潟県上越市)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g2v</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>9/3スギ薬局茜部南店(岐阜市)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g2N</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>9/4クックマート上西店（静岡県浜松市）</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g7N</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>9/4(9/3プレ)スーパー生鮮館TAIGA桂子田店</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>9/4改装 名古屋PARCO</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>9/4改装 メイチカ(名古屋市)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g7g</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>9/4ウルフギャングステーキハウス名古屋店</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1eZr</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>9/4 ゴジラ・ストア Nagoya</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fn6</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>9/4ロピア彦根ナフコ店</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fNK</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>9/10改装 マルナカ檀紙店(香川県高松市)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g7X</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>9/10ザ・ビッグエクスプレスみよし店</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>9/10ファミリーマート中津川下野店</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g84</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>9/11スーパーマーケットバロー豊中島江店</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fXN</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>9/16SANYO Style STORE PLUS イオンモール岡崎店</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1fEw</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>食彩品館NEWS</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>9/17ロピア ムサシ新潟西店(新潟市)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://wp.me/pg0IT6-1g6X</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>9月1日(火)OPEN！「KINUJO」の世界観を五感で楽しむ『KINUJO Cafe &amp; Bar』が銀座の地に誕生。洗練されたインテリアと美食が融合した特別な体験をお届けいたします。</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000048.000094687.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>【2026年9月3日(木)オープン】全国の名品・銘菓を集めた新店舗「日本めぐり はくまる庵」が誕生</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000003.000188020.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>A5黒毛和牛をひつまぶしスタイルで味わう新ランチが誕生。「薪焼きともつ鍋 桂香-KEIKA- 博多西中洲」にて、7月20日（月）より『A5黒毛和牛の博多牛まぶし』の提供を開始</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000019.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>【大阪・天王寺に山椒まぜそば登場】痺れと香りを極めた山椒まぜそば専門店『麺処 山椒』が2026年7月25日（土）グランドオープン！</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000015.000055652.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>新潟市内、フレスポ赤道に登場！ナポリタン専門店「スパゲッティーのパンチョ 新潟赤道店」が7月17日（金）に新規開店、3連続オープニングキャンペーンを開催</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000105.000117096.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>新潟市南区に「あくあしょっぷ　ぎんなん」7月7日OPEN｜海水魚・水草・生体を扱う、小さく始められるアクアリウム専門店</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000002.000186660.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>【オープン記念としておすすめコースに飲み放題を無料提供】香りを愉しむ新業態「薪焼きともつ鍋 桂香-KEIKA- 博多西中洲」が7月6日（月）グランドオープン！7月1日（水）よりプレオープン</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000018.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>栃木初上陸、全国50店舗目の節目を飾る！ナポリタン専門店「スパゲッティーのパンチョ 宇都宮戸祭店」が7月3日（金）に新規開店、3連続オープニングキャンペーンを開催</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000103.000117096.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>【生ビール・角ハイボール・鬼おろしレモンサワー78円】旬を摘まむオトナ酒場「酒と肴 菜の華(なのはな) 銀座通り店」が6月1日(月)グランドオープン！6月30日(火)まで一部ドリンクを破格でご提供！</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000017.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>【和食さと】広島県に初出店！「和食さと広島観音新町店」を2026年5月22日（金）グランドオープン！</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000899.000122416.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>9月1日(火)OPEN！「KINUJO」の世界観を五感で楽しむ『KINUJO Cafe &amp; Bar』が銀座の地に誕生。洗練されたインテリアと美食が融合した特別な体験をお届けいたします。</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000048.000094687.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>【2026年9月3日(木)オープン】全国の名品・銘菓を集めた新店舗「日本めぐり はくまる庵」が誕生</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000003.000188020.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>A5黒毛和牛をひつまぶしスタイルで味わう新ランチが誕生。「薪焼きともつ鍋 桂香-KEIKA- 博多西中洲」にて、7月20日（月）より『A5黒毛和牛の博多牛まぶし』の提供を開始</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000019.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>【大阪・天王寺に山椒まぜそば登場】痺れと香りを極めた山椒まぜそば専門店『麺処 山椒』が2026年7月25日（土）グランドオープン！</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000015.000055652.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>新潟市内、フレスポ赤道に登場！ナポリタン専門店「スパゲッティーのパンチョ 新潟赤道店」が7月17日（金）に新規開店、3連続オープニングキャンペーンを開催</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000105.000117096.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>新潟市南区に「あくあしょっぷ　ぎんなん」7月7日OPEN｜海水魚・水草・生体を扱う、小さく始められるアクアリウム専門店</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000002.000186660.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>【オープン記念としておすすめコースに飲み放題を無料提供】香りを愉しむ新業態「薪焼きともつ鍋 桂香-KEIKA- 博多西中洲」が7月6日（月）グランドオープン！7月1日（水）よりプレオープン</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000018.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>栃木初上陸、全国50店舗目の節目を飾る！ナポリタン専門店「スパゲッティーのパンチョ 宇都宮戸祭店」が7月3日（金）に新規開店、3連続オープニングキャンペーンを開催</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000103.000117096.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>【生ビール・角ハイボール・鬼おろしレモンサワー78円】旬を摘まむオトナ酒場「酒と肴 菜の華(なのはな) 銀座通り店」が6月1日(月)グランドオープン！6月30日(火)まで一部ドリンクを破格でご提供！</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000017.000106843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026年09月07日</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>【和食さと】広島県に初出店！「和食さと広島観音新町店」を2026年5月22日（金）グランドオープン！</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>/main/html/rd/p/000000899.000122416.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
